--- a/May_5_full_log/LHS_HRP_0.01_res.xlsx
+++ b/May_5_full_log/LHS_HRP_0.01_res.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PyCharm\Blueness\May_5_full_log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{902985B9-15B8-48A9-89F4-253C2F433E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53A2EA1-F9CD-46E0-8B27-191F6F6B596F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>HRP</t>
+  </si>
   <si>
     <t>TMB</t>
   </si>
   <si>
     <t>H2O2</t>
+  </si>
+  <si>
+    <t>max_intensity</t>
+  </si>
+  <si>
+    <t>reaction_speed</t>
+  </si>
+  <si>
+    <t>color_retention</t>
   </si>
   <si>
     <t>AUC</t>
@@ -396,10 +408,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -409,362 +421,2966 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
+        <v>0.01</v>
+      </c>
+      <c r="B2">
         <v>0.94544349900000002</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>8.74809E-3</v>
       </c>
-      <c r="C2">
-        <v>10771.06133671743</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D2">
+        <v>100.32639593908659</v>
+      </c>
+      <c r="E2">
+        <v>0.59663865546218486</v>
+      </c>
+      <c r="F2">
+        <v>0.99916819720404926</v>
+      </c>
+      <c r="G2">
+        <v>8365.1317258883319</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.94544349900000002</v>
+      </c>
+      <c r="C3">
+        <v>8.74809E-3</v>
+      </c>
+      <c r="D3">
+        <v>99.686294416243612</v>
+      </c>
+      <c r="E3">
+        <v>0.59663865546218486</v>
+      </c>
+      <c r="F3">
+        <v>0.9991323033679258</v>
+      </c>
+      <c r="G3">
+        <v>8268.1352791878198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>0.01</v>
+      </c>
+      <c r="B4">
+        <v>0.94544349900000002</v>
+      </c>
+      <c r="C4">
+        <v>8.74809E-3</v>
+      </c>
+      <c r="D4">
+        <v>99.286294416243621</v>
+      </c>
+      <c r="E4">
+        <v>0.54621848739495804</v>
+      </c>
+      <c r="F4">
+        <v>0.99886908596378221</v>
+      </c>
+      <c r="G4">
+        <v>7826.0685279187828</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>0.01</v>
+      </c>
+      <c r="B5">
+        <v>0.94544349900000002</v>
+      </c>
+      <c r="C5">
+        <v>8.74809E-3</v>
+      </c>
+      <c r="D5">
+        <v>98.245177664974804</v>
+      </c>
+      <c r="E5">
+        <v>0.52100840336134446</v>
+      </c>
+      <c r="F5">
+        <v>0.99413567010948445</v>
+      </c>
+      <c r="G5">
+        <v>7525.75964467005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>0.01</v>
+      </c>
+      <c r="B6">
         <v>0.67904071399999999</v>
       </c>
-      <c r="B3">
+      <c r="C6">
         <v>0.37511430099999998</v>
       </c>
-      <c r="C3">
-        <v>8674.9894247038919</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4">
+      <c r="D6">
+        <v>95.2091370558378</v>
+      </c>
+      <c r="E6">
+        <v>0.50420168067226889</v>
+      </c>
+      <c r="F6">
+        <v>0.99687889871082691</v>
+      </c>
+      <c r="G6">
+        <v>7062.0875634517824</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>0.01</v>
+      </c>
+      <c r="B7">
+        <v>0.67904071399999999</v>
+      </c>
+      <c r="C7">
+        <v>0.37511430099999998</v>
+      </c>
+      <c r="D7">
+        <v>90.588324873096411</v>
+      </c>
+      <c r="E7">
+        <v>0.47899159663865543</v>
+      </c>
+      <c r="F7">
+        <v>0.99565502440336484</v>
+      </c>
+      <c r="G7">
+        <v>6587.7365482233481</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>0.01</v>
+      </c>
+      <c r="B8">
+        <v>0.38408313900000002</v>
+      </c>
+      <c r="C8">
+        <v>4.2115189999999997E-2</v>
+      </c>
+      <c r="D8">
+        <v>76.867005076142163</v>
+      </c>
+      <c r="E8">
+        <v>0.58823529411764708</v>
+      </c>
+      <c r="F8">
+        <v>0.99548564334205003</v>
+      </c>
+      <c r="G8">
+        <v>6353.8946700507622</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>0.01</v>
+      </c>
+      <c r="B9">
         <v>0.31965575000000002</v>
       </c>
-      <c r="B4">
+      <c r="C9">
         <v>5.5811689999999997E-2</v>
       </c>
-      <c r="C4">
-        <v>8251.2076988155677</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5">
+      <c r="D9">
+        <v>75.970558375634496</v>
+      </c>
+      <c r="E9">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="F9">
+        <v>0.99690235330277577</v>
+      </c>
+      <c r="G9">
+        <v>6234.8035532994936</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>0.01</v>
+      </c>
+      <c r="B10">
+        <v>0.31965575000000002</v>
+      </c>
+      <c r="C10">
+        <v>5.5811689999999997E-2</v>
+      </c>
+      <c r="D10">
+        <v>77.530964467005219</v>
+      </c>
+      <c r="E10">
+        <v>0.56302521008403361</v>
+      </c>
+      <c r="F10">
+        <v>0.99535931280117274</v>
+      </c>
+      <c r="G10">
+        <v>6216.3576142132006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>0.01</v>
+      </c>
+      <c r="B11">
+        <v>0.67904071399999999</v>
+      </c>
+      <c r="C11">
+        <v>0.37511430099999998</v>
+      </c>
+      <c r="D11">
+        <v>84.121827411167203</v>
+      </c>
+      <c r="E11">
+        <v>0.43697478991596639</v>
+      </c>
+      <c r="F11">
+        <v>0.99230147236302368</v>
+      </c>
+      <c r="G11">
+        <v>5896.494416243655</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>0.01</v>
+      </c>
+      <c r="B12">
         <v>0.791226918</v>
       </c>
-      <c r="B5">
+      <c r="C12">
         <v>0.71186704000000001</v>
       </c>
-      <c r="C5">
-        <v>7841.2267343485628</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6">
+      <c r="D12">
+        <v>71.472081218274141</v>
+      </c>
+      <c r="E12">
+        <v>0.54621848739495804</v>
+      </c>
+      <c r="F12">
+        <v>0.99552272727272695</v>
+      </c>
+      <c r="G12">
+        <v>5750.1065989847721</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>0.01</v>
+      </c>
+      <c r="B13">
+        <v>0.67904071399999999</v>
+      </c>
+      <c r="C13">
+        <v>0.37511430099999998</v>
+      </c>
+      <c r="D13">
+        <v>82.02994923857861</v>
+      </c>
+      <c r="E13">
+        <v>0.42016806722689071</v>
+      </c>
+      <c r="F13">
+        <v>0.99281183670690976</v>
+      </c>
+      <c r="G13">
+        <v>5687.6675126903556</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>0.01</v>
+      </c>
+      <c r="B14">
+        <v>0.38408313900000002</v>
+      </c>
+      <c r="C14">
+        <v>4.2115189999999997E-2</v>
+      </c>
+      <c r="D14">
+        <v>69.868527918781751</v>
+      </c>
+      <c r="E14">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="F14">
+        <v>0.99515987242173498</v>
+      </c>
+      <c r="G14">
+        <v>5666.0030456852792</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>0.01</v>
+      </c>
+      <c r="B15">
+        <v>0.791226918</v>
+      </c>
+      <c r="C15">
+        <v>0.71186704000000001</v>
+      </c>
+      <c r="D15">
+        <v>63.597969543147201</v>
+      </c>
+      <c r="E15">
+        <v>0.54621848739495804</v>
+      </c>
+      <c r="F15">
+        <v>0.99413830534448644</v>
+      </c>
+      <c r="G15">
+        <v>5041.1629441624373</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>0.01</v>
+      </c>
+      <c r="B16">
+        <v>0.791226918</v>
+      </c>
+      <c r="C16">
+        <v>0.71186704000000001</v>
+      </c>
+      <c r="D16">
+        <v>62.443654822335027</v>
+      </c>
+      <c r="E16">
+        <v>0.54621848739495804</v>
+      </c>
+      <c r="F16">
+        <v>0.99594192530931425</v>
+      </c>
+      <c r="G16">
+        <v>4878.96649746193</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>0.01</v>
+      </c>
+      <c r="B17">
         <v>0.52872233999999996</v>
       </c>
-      <c r="B6">
+      <c r="C17">
         <v>4.3204617000000001E-2</v>
       </c>
-      <c r="C6">
-        <v>7297.7102368866344</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7">
+      <c r="D17">
+        <v>66.322842639593929</v>
+      </c>
+      <c r="E17">
+        <v>0.45378151260504213</v>
+      </c>
+      <c r="F17">
+        <v>0.99718497428361486</v>
+      </c>
+      <c r="G17">
+        <v>4713.6106598984761</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>0.01</v>
+      </c>
+      <c r="B18">
+        <v>0.52872233999999996</v>
+      </c>
+      <c r="C18">
+        <v>4.3204617000000001E-2</v>
+      </c>
+      <c r="D18">
+        <v>68.759898477157336</v>
+      </c>
+      <c r="E18">
+        <v>0.41176470588235292</v>
+      </c>
+      <c r="F18">
+        <v>0.98917442435606906</v>
+      </c>
+      <c r="G18">
+        <v>4703.6063451776672</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>0.01</v>
+      </c>
+      <c r="B19">
+        <v>0.52872233999999996</v>
+      </c>
+      <c r="C19">
+        <v>4.3204617000000001E-2</v>
+      </c>
+      <c r="D19">
+        <v>67.116243654822341</v>
+      </c>
+      <c r="E19">
+        <v>0.42016806722689071</v>
+      </c>
+      <c r="F19">
+        <v>0.9908394406250236</v>
+      </c>
+      <c r="G19">
+        <v>4623.5845177664987</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>0.01</v>
+      </c>
+      <c r="B20">
+        <v>0.31965575000000002</v>
+      </c>
+      <c r="C20">
+        <v>5.5811689999999997E-2</v>
+      </c>
+      <c r="D20">
+        <v>61.987309644670091</v>
+      </c>
+      <c r="E20">
+        <v>0.46218487394957991</v>
+      </c>
+      <c r="F20">
+        <v>0.98843549113540485</v>
+      </c>
+      <c r="G20">
+        <v>4450.539847715736</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>0.01</v>
+      </c>
+      <c r="B21">
+        <v>0.52872233999999996</v>
+      </c>
+      <c r="C21">
+        <v>4.3204617000000001E-2</v>
+      </c>
+      <c r="D21">
+        <v>61.489340101522863</v>
+      </c>
+      <c r="E21">
+        <v>0.41176470588235292</v>
+      </c>
+      <c r="F21">
+        <v>0.98965773440982696</v>
+      </c>
+      <c r="G21">
+        <v>4168.8256345177679</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>0.01</v>
+      </c>
+      <c r="B22">
+        <v>0.194714374</v>
+      </c>
+      <c r="C22">
+        <v>1.1891000000000001E-2</v>
+      </c>
+      <c r="D22">
+        <v>53.439593908629433</v>
+      </c>
+      <c r="E22">
+        <v>0.55462184873949583</v>
+      </c>
+      <c r="F22">
+        <v>0.99569702496295476</v>
+      </c>
+      <c r="G22">
+        <v>4131.1685279187814</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>0.01</v>
+      </c>
+      <c r="B23">
+        <v>0.153269672</v>
+      </c>
+      <c r="C23">
+        <v>0.105170815</v>
+      </c>
+      <c r="D23">
+        <v>43.178680203045701</v>
+      </c>
+      <c r="E23">
+        <v>0.74789915966386555</v>
+      </c>
+      <c r="F23">
+        <v>0.96242035221367939</v>
+      </c>
+      <c r="G23">
+        <v>4100.45609137056</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>0.01</v>
+      </c>
+      <c r="B24">
+        <v>0.31965575000000002</v>
+      </c>
+      <c r="C24">
+        <v>5.5811689999999997E-2</v>
+      </c>
+      <c r="D24">
+        <v>55.148223350253822</v>
+      </c>
+      <c r="E24">
+        <v>0.45378151260504213</v>
+      </c>
+      <c r="F24">
+        <v>0.99405938771377544</v>
+      </c>
+      <c r="G24">
+        <v>3925.6002538071079</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>0.01</v>
+      </c>
+      <c r="B25">
+        <v>0.791226918</v>
+      </c>
+      <c r="C25">
+        <v>0.71186704000000001</v>
+      </c>
+      <c r="D25">
+        <v>49.216243654822343</v>
+      </c>
+      <c r="E25">
+        <v>0.53781512605042014</v>
+      </c>
+      <c r="F25">
+        <v>0.99325467222245145</v>
+      </c>
+      <c r="G25">
+        <v>3864.8040609137061</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>0.01</v>
+      </c>
+      <c r="B26">
         <v>0.38408313900000002</v>
       </c>
-      <c r="B7">
+      <c r="C26">
         <v>4.2115189999999997E-2</v>
       </c>
-      <c r="C7">
-        <v>6945.5054991539773</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8">
+      <c r="D26">
+        <v>51.826395939086268</v>
+      </c>
+      <c r="E26">
+        <v>0.48739495798319332</v>
+      </c>
+      <c r="F26">
+        <v>0.9964680992771654</v>
+      </c>
+      <c r="G26">
+        <v>3834.9284263959412</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>0.01</v>
+      </c>
+      <c r="B27">
         <v>0.194714374</v>
       </c>
-      <c r="B8">
+      <c r="C27">
         <v>1.1891000000000001E-2</v>
       </c>
-      <c r="C8">
-        <v>6293.2914551607446</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9">
+      <c r="D27">
+        <v>39.198477157360422</v>
+      </c>
+      <c r="E27">
+        <v>0.72268907563025209</v>
+      </c>
+      <c r="F27">
+        <v>0.97568278059077163</v>
+      </c>
+      <c r="G27">
+        <v>3634.0639593908641</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>0.01</v>
+      </c>
+      <c r="B28">
         <v>0.153269672</v>
       </c>
-      <c r="B9">
+      <c r="C28">
         <v>0.105170815</v>
       </c>
-      <c r="C9">
-        <v>5984.7593062605774</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10">
+      <c r="D28">
+        <v>37.971573604060929</v>
+      </c>
+      <c r="E28">
+        <v>0.73109243697478998</v>
+      </c>
+      <c r="F28">
+        <v>0.98024704561253373</v>
+      </c>
+      <c r="G28">
+        <v>3596.1487309644681</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>0.01</v>
+      </c>
+      <c r="B29">
+        <v>0.38408313900000002</v>
+      </c>
+      <c r="C29">
+        <v>4.2115189999999997E-2</v>
+      </c>
+      <c r="D29">
+        <v>47.607614213197991</v>
+      </c>
+      <c r="E29">
+        <v>0.47899159663865543</v>
+      </c>
+      <c r="F29">
+        <v>0.99239979954577928</v>
+      </c>
+      <c r="G29">
+        <v>3482.182233502539</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>0.01</v>
+      </c>
+      <c r="B30">
+        <v>0.153269672</v>
+      </c>
+      <c r="C30">
+        <v>0.105170815</v>
+      </c>
+      <c r="D30">
+        <v>39.203045685279207</v>
+      </c>
+      <c r="E30">
+        <v>0.65546218487394958</v>
+      </c>
+      <c r="F30">
+        <v>0.99421727308040864</v>
+      </c>
+      <c r="G30">
+        <v>3366.781472081218</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>0.01</v>
+      </c>
+      <c r="B31">
+        <v>0.194714374</v>
+      </c>
+      <c r="C31">
+        <v>1.1891000000000001E-2</v>
+      </c>
+      <c r="D31">
+        <v>36.197969543147217</v>
+      </c>
+      <c r="E31">
+        <v>0.69747899159663862</v>
+      </c>
+      <c r="F31">
+        <v>0.98139952320852619</v>
+      </c>
+      <c r="G31">
+        <v>3261.0167512690382</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>0.01</v>
+      </c>
+      <c r="B32">
+        <v>0.153269672</v>
+      </c>
+      <c r="C32">
+        <v>0.105170815</v>
+      </c>
+      <c r="D32">
+        <v>37.178172588832489</v>
+      </c>
+      <c r="E32">
+        <v>0.58823529411764708</v>
+      </c>
+      <c r="F32">
+        <v>0.99493999262708055</v>
+      </c>
+      <c r="G32">
+        <v>3138.421827411169</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>0.01</v>
+      </c>
+      <c r="B33">
         <v>0.28832528499999999</v>
       </c>
-      <c r="B10">
+      <c r="C33">
         <v>0.179584257</v>
       </c>
-      <c r="C10">
-        <v>5360.5926395939096</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11">
+      <c r="D33">
+        <v>40.292385786802029</v>
+      </c>
+      <c r="E33">
+        <v>0.53781512605042014</v>
+      </c>
+      <c r="F33">
+        <v>0.99426526909897184</v>
+      </c>
+      <c r="G33">
+        <v>3096.6159898477172</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>0.01</v>
+      </c>
+      <c r="B34">
+        <v>0.28832528499999999</v>
+      </c>
+      <c r="C34">
+        <v>0.179584257</v>
+      </c>
+      <c r="D34">
+        <v>35.76294416243659</v>
+      </c>
+      <c r="E34">
+        <v>0.52941176470588236</v>
+      </c>
+      <c r="F34">
+        <v>0.99105786836614429</v>
+      </c>
+      <c r="G34">
+        <v>2722.2649746192901</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>0.01</v>
+      </c>
+      <c r="B35">
+        <v>0.194714374</v>
+      </c>
+      <c r="C35">
+        <v>1.1891000000000001E-2</v>
+      </c>
+      <c r="D35">
+        <v>32.92690355329951</v>
+      </c>
+      <c r="E35">
+        <v>0.54621848739495804</v>
+      </c>
+      <c r="F35">
+        <v>0.99243979897018453</v>
+      </c>
+      <c r="G35">
+        <v>2532.9312182741119</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>0.01</v>
+      </c>
+      <c r="B36">
         <v>0.119372969</v>
       </c>
-      <c r="B11">
+      <c r="C36">
         <v>1.6720755E-2</v>
       </c>
-      <c r="C11">
-        <v>4667.9217428088004</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12">
+      <c r="D36">
+        <v>26.26751269035535</v>
+      </c>
+      <c r="E36">
+        <v>0.73109243697478998</v>
+      </c>
+      <c r="F36">
+        <v>0.9887993506869962</v>
+      </c>
+      <c r="G36">
+        <v>2462.7342639593908</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>0.01</v>
+      </c>
+      <c r="B37">
+        <v>6.141945E-2</v>
+      </c>
+      <c r="C37">
+        <v>7.0912129999999999E-3</v>
+      </c>
+      <c r="D37">
+        <v>25.155329949238599</v>
+      </c>
+      <c r="E37">
+        <v>0.76470588235294112</v>
+      </c>
+      <c r="F37">
+        <v>0.9678020824925323</v>
+      </c>
+      <c r="G37">
+        <v>2454.7322335025392</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>0.01</v>
+      </c>
+      <c r="B38">
+        <v>0.119372969</v>
+      </c>
+      <c r="C38">
+        <v>1.6720755E-2</v>
+      </c>
+      <c r="D38">
+        <v>26.715736040609169</v>
+      </c>
+      <c r="E38">
+        <v>0.68907563025210083</v>
+      </c>
+      <c r="F38">
+        <v>0.99041991259737749</v>
+      </c>
+      <c r="G38">
+        <v>2420.6824873096461</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>0.01</v>
+      </c>
+      <c r="B39">
+        <v>0.28832528499999999</v>
+      </c>
+      <c r="C39">
+        <v>0.179584257</v>
+      </c>
+      <c r="D39">
+        <v>32.226395939086302</v>
+      </c>
+      <c r="E39">
+        <v>0.47899159663865543</v>
+      </c>
+      <c r="F39">
+        <v>0.9872223797372649</v>
+      </c>
+      <c r="G39">
+        <v>2410.8106598984782</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>0.01</v>
+      </c>
+      <c r="B40">
         <v>0.18238137099999999</v>
       </c>
-      <c r="B12">
+      <c r="C40">
         <v>1.5524415999999999E-2</v>
       </c>
-      <c r="C12">
-        <v>4472.7343485617603</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13">
+      <c r="D40">
+        <v>26.41928934010156</v>
+      </c>
+      <c r="E40">
+        <v>0.56302521008403361</v>
+      </c>
+      <c r="F40">
+        <v>0.99276793605656466</v>
+      </c>
+      <c r="G40">
+        <v>2140.1220812182751</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>0.01</v>
+      </c>
+      <c r="B41">
+        <v>0.28832528499999999</v>
+      </c>
+      <c r="C41">
+        <v>0.179584257</v>
+      </c>
+      <c r="D41">
+        <v>26.192893401015262</v>
+      </c>
+      <c r="E41">
+        <v>0.44537815126050417</v>
+      </c>
+      <c r="F41">
+        <v>0.9930736434108528</v>
+      </c>
+      <c r="G41">
+        <v>1892.661928934011</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>0.01</v>
+      </c>
+      <c r="B42">
+        <v>0.119372969</v>
+      </c>
+      <c r="C42">
+        <v>1.6720755E-2</v>
+      </c>
+      <c r="D42">
+        <v>21.843147208121842</v>
+      </c>
+      <c r="E42">
+        <v>0.61344537815126055</v>
+      </c>
+      <c r="F42">
+        <v>0.99807115800237001</v>
+      </c>
+      <c r="G42">
+        <v>1870.0644670050769</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>0.01</v>
+      </c>
+      <c r="B43">
+        <v>0.119372969</v>
+      </c>
+      <c r="C43">
+        <v>1.6720755E-2</v>
+      </c>
+      <c r="D43">
+        <v>21.659390862944161</v>
+      </c>
+      <c r="E43">
+        <v>0.6386554621848739</v>
+      </c>
+      <c r="F43">
+        <v>0.99040989945862401</v>
+      </c>
+      <c r="G43">
+        <v>1860.7736040609141</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>0.01</v>
+      </c>
+      <c r="B44">
+        <v>0.18238137099999999</v>
+      </c>
+      <c r="C44">
+        <v>1.5524415999999999E-2</v>
+      </c>
+      <c r="D44">
+        <v>21.69543147208125</v>
+      </c>
+      <c r="E44">
+        <v>0.55462184873949583</v>
+      </c>
+      <c r="F44">
+        <v>0.98435657463734172</v>
+      </c>
+      <c r="G44">
+        <v>1724.4446700507619</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>0.01</v>
+      </c>
+      <c r="B45">
+        <v>0.18238137099999999</v>
+      </c>
+      <c r="C45">
+        <v>1.5524415999999999E-2</v>
+      </c>
+      <c r="D45">
+        <v>23.606091370558371</v>
+      </c>
+      <c r="E45">
+        <v>0.43697478991596639</v>
+      </c>
+      <c r="F45">
+        <v>0.96897471185274486</v>
+      </c>
+      <c r="G45">
+        <v>1701.7677664974631</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>0.01</v>
+      </c>
+      <c r="B46">
         <v>0.10962591200000001</v>
       </c>
-      <c r="B13">
+      <c r="C46">
         <v>3.3106069000000002E-2</v>
       </c>
-      <c r="C13">
-        <v>4105.3637901861257</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14">
+      <c r="D46">
+        <v>16.418781725888319</v>
+      </c>
+      <c r="E46">
+        <v>0.80672268907563027</v>
+      </c>
+      <c r="F46">
+        <v>0.83011902921626302</v>
+      </c>
+      <c r="G46">
+        <v>1532.7225888324881</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>0.01</v>
+      </c>
+      <c r="B47">
+        <v>0.10962591200000001</v>
+      </c>
+      <c r="C47">
+        <v>3.3106069000000002E-2</v>
+      </c>
+      <c r="D47">
+        <v>17.239086294416261</v>
+      </c>
+      <c r="E47">
+        <v>0.68907563025210083</v>
+      </c>
+      <c r="F47">
+        <v>0.94020788551573742</v>
+      </c>
+      <c r="G47">
+        <v>1519.9977157360411</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>0.01</v>
+      </c>
+      <c r="B48">
         <v>6.141945E-2</v>
       </c>
-      <c r="B14">
+      <c r="C48">
         <v>7.0912129999999999E-3</v>
       </c>
-      <c r="C14">
-        <v>4029.927241962775</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15">
+      <c r="D48">
+        <v>14.745177664974641</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>1514.042893401017</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>0.01</v>
+      </c>
+      <c r="B49">
         <v>8.2327229000000002E-2</v>
       </c>
-      <c r="B15">
+      <c r="C49">
         <v>0.44450251899999998</v>
       </c>
-      <c r="C15">
-        <v>3956.5346869712362</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16">
+      <c r="D49">
+        <v>15.1746192893401</v>
+      </c>
+      <c r="E49">
+        <v>0.74789915966386555</v>
+      </c>
+      <c r="F49">
+        <v>0.94548738877366623</v>
+      </c>
+      <c r="G49">
+        <v>1416.5063451776659</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>0.01</v>
+      </c>
+      <c r="B50">
+        <v>0.10962591200000001</v>
+      </c>
+      <c r="C50">
+        <v>3.3106069000000002E-2</v>
+      </c>
+      <c r="D50">
+        <v>14.81725888324873</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>1409.515482233503</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>0.01</v>
+      </c>
+      <c r="B51">
+        <v>6.141945E-2</v>
+      </c>
+      <c r="C51">
+        <v>7.0912129999999999E-3</v>
+      </c>
+      <c r="D51">
+        <v>13.88274111675128</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>1391.1350253807111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>0.01</v>
+      </c>
+      <c r="B52">
+        <v>6.141945E-2</v>
+      </c>
+      <c r="C52">
+        <v>7.0912129999999999E-3</v>
+      </c>
+      <c r="D52">
+        <v>12.834010152284289</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>1332.3873096446709</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>0.01</v>
+      </c>
+      <c r="B53">
+        <v>8.2327229000000002E-2</v>
+      </c>
+      <c r="C53">
+        <v>0.44450251899999998</v>
+      </c>
+      <c r="D53">
+        <v>14.217258883248739</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>1316.784263959391</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>0.01</v>
+      </c>
+      <c r="B54">
+        <v>8.2327229000000002E-2</v>
+      </c>
+      <c r="C54">
+        <v>0.44450251899999998</v>
+      </c>
+      <c r="D54">
+        <v>13.61370558375636</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>1283.549746192894</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>0.01</v>
+      </c>
+      <c r="B55">
+        <v>0.10962591200000001</v>
+      </c>
+      <c r="C55">
+        <v>3.3106069000000002E-2</v>
+      </c>
+      <c r="D55">
+        <v>13.942639593908639</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>1205.9380710659909</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>0.01</v>
+      </c>
+      <c r="B56">
         <v>0.50502969600000003</v>
       </c>
-      <c r="B16">
+      <c r="C56">
         <v>7.4037125999999995E-2</v>
       </c>
-      <c r="C16">
-        <v>3516.473350253807</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17">
+      <c r="D56">
+        <v>15.416243654822351</v>
+      </c>
+      <c r="E56">
+        <v>0.53781512605042014</v>
+      </c>
+      <c r="F56">
+        <v>0.99419163648337205</v>
+      </c>
+      <c r="G56">
+        <v>1153.4446700507619</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>0.01</v>
+      </c>
+      <c r="B57">
+        <v>8.2327229000000002E-2</v>
+      </c>
+      <c r="C57">
+        <v>0.44450251899999998</v>
+      </c>
+      <c r="D57">
+        <v>11.92639593908628</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>1103.9695431472089</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>0.01</v>
+      </c>
+      <c r="B58">
+        <v>0.50502969600000003</v>
+      </c>
+      <c r="C58">
+        <v>7.4037125999999995E-2</v>
+      </c>
+      <c r="D58">
+        <v>14.37005076142132</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>1088.001776649746</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>0.01</v>
+      </c>
+      <c r="B59">
+        <v>0.18238137099999999</v>
+      </c>
+      <c r="C59">
+        <v>1.5524415999999999E-2</v>
+      </c>
+      <c r="D59">
+        <v>13.3756345177665</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>1006.583502538072</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>0.01</v>
+      </c>
+      <c r="B60">
+        <v>0.50502969600000003</v>
+      </c>
+      <c r="C60">
+        <v>7.4037125999999995E-2</v>
+      </c>
+      <c r="D60">
+        <v>11.754822335025359</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>815.0850253807115</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>0.01</v>
+      </c>
+      <c r="B61">
+        <v>0.50502969600000003</v>
+      </c>
+      <c r="C61">
+        <v>7.4037125999999995E-2</v>
+      </c>
+      <c r="D61">
+        <v>11.02487309644672</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>794.03502538071132</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>0.01</v>
+      </c>
+      <c r="B62">
         <v>4.3358882000000001E-2</v>
       </c>
-      <c r="B17">
+      <c r="C62">
         <v>1.0798904E-2</v>
       </c>
-      <c r="C17">
-        <v>3246.9483925549921</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18">
+      <c r="D62">
+        <v>8.3319796954314995</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>698.17766497462026</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>0.01</v>
+      </c>
+      <c r="B63">
+        <v>4.3358882000000001E-2</v>
+      </c>
+      <c r="C63">
+        <v>1.0798904E-2</v>
+      </c>
+      <c r="D63">
+        <v>7.7715736040609222</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>645.33223350253832</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>0.01</v>
+      </c>
+      <c r="B64">
+        <v>3.7493000999999998E-2</v>
+      </c>
+      <c r="C64">
+        <v>0.32625970999999998</v>
+      </c>
+      <c r="D64">
+        <v>7.0563451776649586</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>644.67411167512819</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>0.01</v>
+      </c>
+      <c r="B65">
+        <v>0.23554819099999999</v>
+      </c>
+      <c r="C65">
+        <v>0.91044763100000003</v>
+      </c>
+      <c r="D65">
+        <v>9.5324873096446865</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>643.65380710659963</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>0.01</v>
+      </c>
+      <c r="B66">
         <v>1.5814747000000001E-2</v>
       </c>
-      <c r="B18">
+      <c r="C66">
         <v>0.13384248000000001</v>
       </c>
-      <c r="C18">
-        <v>3222.7343485617598</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19">
+      <c r="D66">
+        <v>6.5076142131979822</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>618.1032994923861</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>0.01</v>
+      </c>
+      <c r="B67">
+        <v>1.5814747000000001E-2</v>
+      </c>
+      <c r="C67">
+        <v>0.13384248000000001</v>
+      </c>
+      <c r="D67">
+        <v>6.3076142131979793</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>614.2279187817262</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>0.01</v>
+      </c>
+      <c r="B68">
+        <v>1.5814747000000001E-2</v>
+      </c>
+      <c r="C68">
+        <v>0.13384248000000001</v>
+      </c>
+      <c r="D68">
+        <v>5.9573604060913823</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>583.12385786802099</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>0.01</v>
+      </c>
+      <c r="B69">
         <v>3.7493000999999998E-2</v>
       </c>
-      <c r="B19">
+      <c r="C69">
         <v>0.32625970999999998</v>
       </c>
-      <c r="C19">
-        <v>3217.2923011844341</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20">
+      <c r="D69">
+        <v>6.4883248730964604</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>582.45964467005103</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>0.01</v>
+      </c>
+      <c r="B70">
+        <v>3.7493000999999998E-2</v>
+      </c>
+      <c r="C70">
+        <v>0.32625970999999998</v>
+      </c>
+      <c r="D70">
+        <v>6.5614213197969598</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>572.31878172588893</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>0.01</v>
+      </c>
+      <c r="B71">
         <v>0.23554819099999999</v>
       </c>
-      <c r="B20">
+      <c r="C71">
         <v>0.91044763100000003</v>
       </c>
-      <c r="C20">
-        <v>3132.7089678511002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21">
+      <c r="D71">
+        <v>8.0979695431472187</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>553.23908629441723</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>0.01</v>
+      </c>
+      <c r="B72">
+        <v>4.3358882000000001E-2</v>
+      </c>
+      <c r="C72">
+        <v>1.0798904E-2</v>
+      </c>
+      <c r="D72">
+        <v>6.8091370558375637</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>543.78730964467036</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>0.01</v>
+      </c>
+      <c r="B73">
+        <v>1.5814747000000001E-2</v>
+      </c>
+      <c r="C73">
+        <v>0.13384248000000001</v>
+      </c>
+      <c r="D73">
+        <v>6.0878172588832626</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>539.84847715736112</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>0.01</v>
+      </c>
+      <c r="B74">
+        <v>0.23554819099999999</v>
+      </c>
+      <c r="C74">
+        <v>0.91044763100000003</v>
+      </c>
+      <c r="D74">
+        <v>7.7401015228426431</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>528.33781725888343</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>0.01</v>
+      </c>
+      <c r="B75">
         <v>9.8940220000000006E-3</v>
       </c>
-      <c r="B21">
+      <c r="C75">
         <v>2.8952749999999999E-2</v>
       </c>
-      <c r="C21">
-        <v>3119.7868020304568</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22">
+      <c r="D75">
+        <v>6.2908629441624413</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>526.17309644670115</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>0.01</v>
+      </c>
+      <c r="B76">
+        <v>9.8940220000000006E-3</v>
+      </c>
+      <c r="C76">
+        <v>2.8952749999999999E-2</v>
+      </c>
+      <c r="D76">
+        <v>5.6380710659898634</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>515.97182741116762</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>0.01</v>
+      </c>
+      <c r="B77">
         <v>9.4825337999999995E-2</v>
       </c>
-      <c r="B22">
+      <c r="C77">
         <v>6.8822579999999994E-2</v>
       </c>
-      <c r="C22">
-        <v>3090.0156514382402</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23">
+      <c r="D77">
+        <v>6.061421319796942</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>499.55507614213218</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>0.01</v>
+      </c>
+      <c r="B78">
+        <v>3.7493000999999998E-2</v>
+      </c>
+      <c r="C78">
+        <v>0.32625970999999998</v>
+      </c>
+      <c r="D78">
+        <v>5.8218274111675221</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>498.53147208121868</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>0.01</v>
+      </c>
+      <c r="B79">
+        <v>9.4825337999999995E-2</v>
+      </c>
+      <c r="C79">
+        <v>6.8822579999999994E-2</v>
+      </c>
+      <c r="D79">
+        <v>5.735532994923858</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>469.58248730964448</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>0.01</v>
+      </c>
+      <c r="B80">
         <v>5.1799179000000001E-2</v>
       </c>
-      <c r="B23">
+      <c r="C80">
         <v>0.20548492600000001</v>
       </c>
-      <c r="C23">
-        <v>3044.6006768189509</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24">
+      <c r="D80">
+        <v>5.1040609137055766</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>467.16345177664982</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>0.01</v>
+      </c>
+      <c r="B81">
+        <v>9.8940220000000006E-3</v>
+      </c>
+      <c r="C81">
+        <v>2.8952749999999999E-2</v>
+      </c>
+      <c r="D81">
+        <v>5.3609137055837408</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>465.3530456852792</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>0.01</v>
+      </c>
+      <c r="B82">
+        <v>0.23554819099999999</v>
+      </c>
+      <c r="C82">
+        <v>0.91044763100000003</v>
+      </c>
+      <c r="D82">
+        <v>6.6451776649746179</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>463.23553299492443</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>0.01</v>
+      </c>
+      <c r="B83">
+        <v>9.4825337999999995E-2</v>
+      </c>
+      <c r="C83">
+        <v>6.8822579999999994E-2</v>
+      </c>
+      <c r="D83">
+        <v>5.6324873096446666</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>448.53248730964492</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>0.01</v>
+      </c>
+      <c r="B84">
+        <v>9.8940220000000006E-3</v>
+      </c>
+      <c r="C84">
+        <v>2.8952749999999999E-2</v>
+      </c>
+      <c r="D84">
+        <v>4.974111675126899</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>444.8982233502548</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>0.01</v>
+      </c>
+      <c r="B85">
         <v>3.1271981999999997E-2</v>
       </c>
-      <c r="B24">
+      <c r="C85">
         <v>0.157239723</v>
       </c>
-      <c r="C24">
-        <v>3025.567258883249</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25">
+      <c r="D85">
+        <v>5.2380710659898249</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>433.95456852791932</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>0.01</v>
+      </c>
+      <c r="B86">
+        <v>5.1799179000000001E-2</v>
+      </c>
+      <c r="C86">
+        <v>0.20548492600000001</v>
+      </c>
+      <c r="D86">
+        <v>5.1360406091370834</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>429.11827411167559</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>0.01</v>
+      </c>
+      <c r="B87">
+        <v>3.1271981999999997E-2</v>
+      </c>
+      <c r="C87">
+        <v>0.157239723</v>
+      </c>
+      <c r="D87">
+        <v>4.9020304568528026</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>418.44923857868088</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>0.01</v>
+      </c>
+      <c r="B88">
+        <v>3.1271981999999997E-2</v>
+      </c>
+      <c r="C88">
+        <v>0.157239723</v>
+      </c>
+      <c r="D88">
+        <v>5.2736040609137049</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>406.45253807106678</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>0.01</v>
+      </c>
+      <c r="B89">
+        <v>4.3358882000000001E-2</v>
+      </c>
+      <c r="C89">
+        <v>1.0798904E-2</v>
+      </c>
+      <c r="D89">
+        <v>4.9659898477157611</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>401.52868020304652</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>0.01</v>
+      </c>
+      <c r="B90">
+        <v>3.1271981999999997E-2</v>
+      </c>
+      <c r="C90">
+        <v>0.157239723</v>
+      </c>
+      <c r="D90">
+        <v>4.6304568527918804</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>398.73756345177719</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>0.01</v>
+      </c>
+      <c r="B91">
+        <v>9.4825337999999995E-2</v>
+      </c>
+      <c r="C91">
+        <v>6.8822579999999994E-2</v>
+      </c>
+      <c r="D91">
+        <v>4.9263959390862979</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>397.02868020304612</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>0.01</v>
+      </c>
+      <c r="B92">
+        <v>5.1799179000000001E-2</v>
+      </c>
+      <c r="C92">
+        <v>0.20548492600000001</v>
+      </c>
+      <c r="D92">
+        <v>4.6939086294416228</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>385.91472081218308</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>0.01</v>
+      </c>
+      <c r="B93">
+        <v>2.3732152999999999E-2</v>
+      </c>
+      <c r="C93">
+        <v>5.8438759999999996E-3</v>
+      </c>
+      <c r="D93">
+        <v>4.7197969543147424</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>362.54822335025472</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>0.01</v>
+      </c>
+      <c r="B94">
         <v>8.0754169999999997E-3</v>
       </c>
-      <c r="B25">
+      <c r="C94">
         <v>2.2905526999999998E-2</v>
       </c>
-      <c r="C25">
-        <v>2856.896362098139</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26">
+      <c r="D94">
+        <v>4.0695431472081438</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>345.57055837563519</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>0.01</v>
+      </c>
+      <c r="B95">
+        <v>5.1799179000000001E-2</v>
+      </c>
+      <c r="C95">
+        <v>0.20548492600000001</v>
+      </c>
+      <c r="D95">
+        <v>3.8395939086294431</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>333.76649746192919</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>0.01</v>
+      </c>
+      <c r="B96">
         <v>1.9470609999999999E-2</v>
       </c>
-      <c r="B26">
+      <c r="C96">
         <v>6.5729339999999999E-3</v>
       </c>
-      <c r="C26">
-        <v>2820.6713197969548</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27">
+      <c r="D96">
+        <v>3.6137055837563419</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>280.95558375634539</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>0.01</v>
+      </c>
+      <c r="B97">
+        <v>1.9470609999999999E-2</v>
+      </c>
+      <c r="C97">
+        <v>6.5729339999999999E-3</v>
+      </c>
+      <c r="D97">
+        <v>3.4918781725888408</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>269.22106598984811</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>0.01</v>
+      </c>
+      <c r="B98">
+        <v>8.0754169999999997E-3</v>
+      </c>
+      <c r="C98">
+        <v>2.2905526999999998E-2</v>
+      </c>
+      <c r="D98">
+        <v>3.2568527918781629</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>260.32842639593929</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>0.01</v>
+      </c>
+      <c r="B99">
+        <v>8.0754169999999997E-3</v>
+      </c>
+      <c r="C99">
+        <v>2.2905526999999998E-2</v>
+      </c>
+      <c r="D99">
+        <v>2.968527918781724</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>250.3573604060918</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>0.01</v>
+      </c>
+      <c r="B100">
         <v>2.3732152999999999E-2</v>
       </c>
-      <c r="B27">
+      <c r="C100">
         <v>5.8438759999999996E-3</v>
       </c>
-      <c r="C27">
-        <v>2772.9877326565152</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28">
+      <c r="D100">
+        <v>3.7319796954315052</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>235.717258883249</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>0.01</v>
+      </c>
+      <c r="B101">
+        <v>5.2313739999999996E-3</v>
+      </c>
+      <c r="C101">
+        <v>0.22555581799999999</v>
+      </c>
+      <c r="D101">
+        <v>2.7203045685279221</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>229.33730964467031</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>0.01</v>
+      </c>
+      <c r="B102">
+        <v>8.0754169999999997E-3</v>
+      </c>
+      <c r="C102">
+        <v>2.2905526999999998E-2</v>
+      </c>
+      <c r="D102">
+        <v>2.6507614213198032</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>208.02588832487339</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>0.01</v>
+      </c>
+      <c r="B103">
+        <v>1.9470609999999999E-2</v>
+      </c>
+      <c r="C103">
+        <v>6.5729339999999999E-3</v>
+      </c>
+      <c r="D103">
+        <v>2.4949238578680411</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>176.996700507615</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>0.01</v>
+      </c>
+      <c r="B104">
+        <v>5.2313739999999996E-3</v>
+      </c>
+      <c r="C104">
+        <v>0.22555581799999999</v>
+      </c>
+      <c r="D104">
+        <v>2.211167512690341</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>173.18604060913751</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>0.01</v>
+      </c>
+      <c r="B105">
+        <v>1.9470609999999999E-2</v>
+      </c>
+      <c r="C105">
+        <v>6.5729339999999999E-3</v>
+      </c>
+      <c r="D105">
+        <v>2.55076142131982</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>164.56294416243711</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>0.01</v>
+      </c>
+      <c r="B106">
         <v>1.2949861999999999E-2</v>
       </c>
-      <c r="B28">
+      <c r="C106">
         <v>0.27340945700000002</v>
       </c>
-      <c r="C28">
-        <v>2752.4648900169209</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29">
+      <c r="D106">
+        <v>2.1527918781725819</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>153.6256345177666</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>0.01</v>
+      </c>
+      <c r="B107">
+        <v>1.2949861999999999E-2</v>
+      </c>
+      <c r="C107">
+        <v>0.27340945700000002</v>
+      </c>
+      <c r="D107">
+        <v>2.1573604060913598</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>142.4840101522843</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>0.01</v>
+      </c>
+      <c r="B108">
         <v>5.2313739999999996E-3</v>
       </c>
-      <c r="B29">
+      <c r="C108">
         <v>0.22555581799999999</v>
       </c>
-      <c r="C29">
-        <v>2750.743654822335</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30">
+      <c r="D108">
+        <v>1.838071065989858</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>137.31116751269099</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>0.01</v>
+      </c>
+      <c r="B109">
+        <v>2.3732152999999999E-2</v>
+      </c>
+      <c r="C109">
+        <v>5.8438759999999996E-3</v>
+      </c>
+      <c r="D109">
+        <v>2.733502538071082</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>134.61725888324929</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>0.01</v>
+      </c>
+      <c r="B110">
+        <v>1.2949861999999999E-2</v>
+      </c>
+      <c r="C110">
+        <v>0.27340945700000002</v>
+      </c>
+      <c r="D110">
+        <v>2.00406091370558</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>134.33908629441609</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>0.01</v>
+      </c>
+      <c r="B111">
+        <v>1.2949861999999999E-2</v>
+      </c>
+      <c r="C111">
+        <v>0.27340945700000002</v>
+      </c>
+      <c r="D111">
+        <v>1.9695431472081419</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>129.0994923857873</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>0.01</v>
+      </c>
+      <c r="B112">
         <v>8.4074679999999995E-3</v>
       </c>
-      <c r="B30">
+      <c r="C112">
         <v>8.5871073000000006E-2</v>
       </c>
-      <c r="C30">
-        <v>2695.9505076142141</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31">
+      <c r="D112">
+        <v>1.7248730964467001</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>114.28654822335059</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>0.01</v>
+      </c>
+      <c r="B113">
+        <v>8.4074679999999995E-3</v>
+      </c>
+      <c r="C113">
+        <v>8.5871073000000006E-2</v>
+      </c>
+      <c r="D113">
+        <v>1.6629441624365631</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>97.196446700508091</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>0.01</v>
+      </c>
+      <c r="B114">
+        <v>2.3732152999999999E-2</v>
+      </c>
+      <c r="C114">
+        <v>5.8438759999999996E-3</v>
+      </c>
+      <c r="D114">
+        <v>2.3152284263959402</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>96.392385786802038</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>0.01</v>
+      </c>
+      <c r="B115">
+        <v>5.2313739999999996E-3</v>
+      </c>
+      <c r="C115">
+        <v>0.22555581799999999</v>
+      </c>
+      <c r="D115">
+        <v>1.5913705583756439</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>89.284771573604459</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>0.01</v>
+      </c>
+      <c r="B116">
+        <v>8.4074679999999995E-3</v>
+      </c>
+      <c r="C116">
+        <v>8.5871073000000006E-2</v>
+      </c>
+      <c r="D116">
+        <v>1.818781725888321</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <v>74.021319796954643</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>0.01</v>
+      </c>
+      <c r="B117">
+        <v>8.4074679999999995E-3</v>
+      </c>
+      <c r="C117">
+        <v>8.5871073000000006E-2</v>
+      </c>
+      <c r="D117">
+        <v>1.415736040609143</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>65.296446700507715</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>0.01</v>
+      </c>
+      <c r="B118">
         <v>1.6129300999999999E-2</v>
       </c>
-      <c r="B31">
+      <c r="C118">
         <v>0.80340095</v>
       </c>
-      <c r="C31">
-        <v>2613.8468697123521</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32">
+      <c r="D118">
+        <v>1.5964467005076199</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>46.79949238578692</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>0.01</v>
+      </c>
+      <c r="B119">
+        <v>1.6129300999999999E-2</v>
+      </c>
+      <c r="C119">
+        <v>0.80340095</v>
+      </c>
+      <c r="D119">
+        <v>1.3294416243655041</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>10.23604060913684</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>0.01</v>
+      </c>
+      <c r="B120">
+        <v>1.6129300999999999E-2</v>
+      </c>
+      <c r="C120">
+        <v>0.80340095</v>
+      </c>
+      <c r="D120">
+        <v>0.92284263959390245</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>-67.735025380710013</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>0.01</v>
+      </c>
+      <c r="B121">
+        <v>1.6129300999999999E-2</v>
+      </c>
+      <c r="C121">
+        <v>0.80340095</v>
+      </c>
+      <c r="D121">
+        <v>-2.0304568527755862E-3</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>-131.449746192893</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>0.01</v>
+      </c>
+      <c r="B122">
         <v>6.1348319999999998E-3</v>
       </c>
-      <c r="B32">
+      <c r="C122">
         <v>2.128919E-2</v>
       </c>
-      <c r="C32">
-        <v>2355.1167512690349</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33">
+      <c r="D122">
+        <v>-0.51878172588831717</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>-141.88908629441531</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>0.01</v>
+      </c>
+      <c r="B123">
+        <v>6.1348319999999998E-3</v>
+      </c>
+      <c r="C123">
+        <v>2.128919E-2</v>
+      </c>
+      <c r="D123">
+        <v>-1.535532994923855</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>-233.19289340101511</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>0.01</v>
+      </c>
+      <c r="B124">
+        <v>6.1348319999999998E-3</v>
+      </c>
+      <c r="C124">
+        <v>2.128919E-2</v>
+      </c>
+      <c r="D124">
+        <v>-1.4477157360406001</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>-256.26852791878088</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>0.01</v>
+      </c>
+      <c r="B125">
         <v>2.9451677999999998E-2</v>
       </c>
-      <c r="B33">
+      <c r="C125">
         <v>0.527671479</v>
       </c>
-      <c r="C33">
-        <v>2175.7411167512691</v>
+      <c r="D125">
+        <v>-1.412690355329943</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="G125">
+        <v>-257.83020304568493</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>0.01</v>
+      </c>
+      <c r="B126">
+        <v>6.1348319999999998E-3</v>
+      </c>
+      <c r="C126">
+        <v>2.128919E-2</v>
+      </c>
+      <c r="D126">
+        <v>-1.807106598984781</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <v>-297.67131979695381</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>0.01</v>
+      </c>
+      <c r="B127">
+        <v>2.9451677999999998E-2</v>
+      </c>
+      <c r="C127">
+        <v>0.527671479</v>
+      </c>
+      <c r="D127">
+        <v>-2.4086294416243561</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127">
+        <v>-392.20532994923781</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>0.01</v>
+      </c>
+      <c r="B128">
+        <v>2.9451677999999998E-2</v>
+      </c>
+      <c r="C128">
+        <v>0.527671479</v>
+      </c>
+      <c r="D128">
+        <v>-3.1588832487309588</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128">
+        <v>-460.54035532994908</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>0.01</v>
+      </c>
+      <c r="B129">
+        <v>2.9451677999999998E-2</v>
+      </c>
+      <c r="C129">
+        <v>0.527671479</v>
+      </c>
+      <c r="D129">
+        <v>-3.24619289340102</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+      <c r="G129">
+        <v>-471.68248730964478</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C33">
-    <sortCondition descending="1" ref="C1:C33"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G129">
+    <sortCondition descending="1" ref="G1:G129"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/May_5_full_log/LHS_HRP_0.01_res.xlsx
+++ b/May_5_full_log/LHS_HRP_0.01_res.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PyCharm\Blueness\May_5_full_log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53A2EA1-F9CD-46E0-8B27-191F6F6B596F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27238675-DDC2-49B4-BB21-053E85D14152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1506,10 +1506,10 @@
         <v>14.745177664974641</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>0.85714285714285721</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>0.89982787110988749</v>
       </c>
       <c r="G48">
         <v>1514.042893401017</v>
@@ -1552,10 +1552,10 @@
         <v>14.81725888324873</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>0.81512605042016806</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>0.8726139088729028</v>
       </c>
       <c r="G50">
         <v>1409.515482233503</v>
@@ -1575,10 +1575,10 @@
         <v>13.88274111675128</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>0.84033613445378152</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>0.90883761746316105</v>
       </c>
       <c r="G51">
         <v>1391.1350253807111</v>
@@ -1598,10 +1598,10 @@
         <v>12.834010152284289</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>0.85714285714285721</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>0.94457145117272234</v>
       </c>
       <c r="G52">
         <v>1332.3873096446709</v>
@@ -1621,10 +1621,10 @@
         <v>14.217258883248739</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>0.74789915966386555</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>0.92834904313053568</v>
       </c>
       <c r="G53">
         <v>1316.784263959391</v>
@@ -1644,10 +1644,10 @@
         <v>13.61370558375636</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>0.78151260504201681</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>0.92119020097691717</v>
       </c>
       <c r="G54">
         <v>1283.549746192894</v>
@@ -1667,10 +1667,10 @@
         <v>13.942639593908639</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>0.91712236501984157</v>
       </c>
       <c r="G55">
         <v>1205.9380710659909</v>
@@ -1713,10 +1713,10 @@
         <v>11.92639593908628</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>0.73949579831932777</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>0.94773356033198608</v>
       </c>
       <c r="G57">
         <v>1103.9695431472089</v>
@@ -1736,10 +1736,10 @@
         <v>14.37005076142132</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>0.53781512605042014</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>0.98442191529195699</v>
       </c>
       <c r="G58">
         <v>1088.001776649746</v>
@@ -1759,10 +1759,10 @@
         <v>13.3756345177665</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>0.47058823529411759</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>0.98213282732447826</v>
       </c>
       <c r="G59">
         <v>1006.583502538072</v>
@@ -1782,10 +1782,10 @@
         <v>11.754822335025359</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>0.44537815126050417</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>0.99039599257244182</v>
       </c>
       <c r="G60">
         <v>815.0850253807115</v>
@@ -1805,10 +1805,10 @@
         <v>11.02487309644672</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>0.43697478991596639</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>0.9958745798609514</v>
       </c>
       <c r="G61">
         <v>794.03502538071132</v>
@@ -1828,10 +1828,10 @@
         <v>8.3319796954314995</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>0.81512605042016806</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>0.70929694163518797</v>
       </c>
       <c r="G62">
         <v>698.17766497462026</v>
@@ -1851,10 +1851,10 @@
         <v>7.7715736040609222</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>0.73949579831932777</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>0.7708948399738722</v>
       </c>
       <c r="G63">
         <v>645.33223350253832</v>
@@ -1874,10 +1874,10 @@
         <v>7.0563451776649586</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>0.73949579831932777</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>0.97631825048558174</v>
       </c>
       <c r="G64">
         <v>644.67411167512819</v>
@@ -1897,10 +1897,10 @@
         <v>9.5324873096446865</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>0.47058823529411759</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>0.99622983119441988</v>
       </c>
       <c r="G65">
         <v>643.65380710659963</v>
@@ -1920,10 +1920,10 @@
         <v>6.5076142131979822</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>0.83193277310924363</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>0.76173166926677172</v>
       </c>
       <c r="G66">
         <v>618.1032994923861</v>
@@ -1943,10 +1943,10 @@
         <v>6.3076142131979793</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>0.84873949579831931</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>0.82082729760180062</v>
       </c>
       <c r="G67">
         <v>614.2279187817262</v>
@@ -1966,10 +1966,10 @@
         <v>5.9573604060913823</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>0.83193277310924363</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>0.87629516019086207</v>
       </c>
       <c r="G68">
         <v>583.12385786802099</v>
@@ -1989,10 +1989,10 @@
         <v>6.4883248730964604</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>0.76470588235294112</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>0.97044281020184686</v>
       </c>
       <c r="G69">
         <v>582.45964467005103</v>
@@ -2012,10 +2012,10 @@
         <v>6.5614213197969598</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>0.94878539377997839</v>
       </c>
       <c r="G70">
         <v>572.31878172588893</v>
@@ -2035,10 +2035,10 @@
         <v>8.0979695431472187</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>0.42016806722689071</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>0.98465492383877673</v>
       </c>
       <c r="G71">
         <v>553.23908629441723</v>
@@ -2058,10 +2058,10 @@
         <v>6.8091370558375637</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>0.76470588235294112</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>0.71335917697927709</v>
       </c>
       <c r="G72">
         <v>543.78730964467036</v>
@@ -2081,10 +2081,10 @@
         <v>6.0878172588832626</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>0.83193277310924363</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>0.74014841991161273</v>
       </c>
       <c r="G73">
         <v>539.84847715736112</v>
@@ -2104,10 +2104,10 @@
         <v>7.7401015228426431</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>0.47899159663865543</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>0.97621983210912944</v>
       </c>
       <c r="G74">
         <v>528.33781725888343</v>
@@ -2127,10 +2127,10 @@
         <v>6.2908629441624413</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>0.86554621848739499</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>0.62462680545469174</v>
       </c>
       <c r="G75">
         <v>526.17309644670115</v>
@@ -2150,10 +2150,10 @@
         <v>5.6380710659898634</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>0.91596638655462181</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>0.70802196812820639</v>
       </c>
       <c r="G76">
         <v>515.97182741116762</v>
@@ -2173,10 +2173,10 @@
         <v>6.061421319796942</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>0.68067226890756305</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>0.97392178209530089</v>
       </c>
       <c r="G77">
         <v>499.55507614213218</v>
@@ -2196,10 +2196,10 @@
         <v>5.8218274111675221</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>0.93528642427412989</v>
       </c>
       <c r="G78">
         <v>498.53147208121868</v>
@@ -2219,10 +2219,10 @@
         <v>5.735532994923858</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>0.68067226890756305</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>0.96576688202495797</v>
       </c>
       <c r="G79">
         <v>469.58248730964448</v>
@@ -2242,10 +2242,10 @@
         <v>5.1040609137055766</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>0.74789915966386555</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>0.92362008950770802</v>
       </c>
       <c r="G80">
         <v>467.16345177664982</v>
@@ -2265,10 +2265,10 @@
         <v>5.3609137055837408</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>0.89915966386554624</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>0.5851529211248977</v>
       </c>
       <c r="G81">
         <v>465.3530456852792</v>
@@ -2288,10 +2288,10 @@
         <v>6.6451776649746179</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>0.56302521008403361</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>0.98221679016118135</v>
       </c>
       <c r="G82">
         <v>463.23553299492443</v>
@@ -2311,10 +2311,10 @@
         <v>5.6324873096446666</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>0.66386554621848737</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>0.9626351838500351</v>
       </c>
       <c r="G83">
         <v>448.53248730964492</v>
@@ -2357,10 +2357,10 @@
         <v>5.2380710659898249</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>0.9536970636689599</v>
       </c>
       <c r="G85">
         <v>433.95456852791932</v>
@@ -2380,10 +2380,10 @@
         <v>5.1360406091370834</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>0.68907563025210083</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>0.97274164854714062</v>
       </c>
       <c r="G86">
         <v>429.11827411167559</v>
@@ -2426,10 +2426,10 @@
         <v>5.2736040609137049</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>0.67226890756302526</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>0.95464433535470561</v>
       </c>
       <c r="G88">
         <v>406.45253807106678</v>
